--- a/labs/lab-05-design-and-build/data/Northstar_Work_Orders.xlsx
+++ b/labs/lab-05-design-and-build/data/Northstar_Work_Orders.xlsx
@@ -510,7 +510,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Northstar Facilities - fictional</t>
+          <t>Northstar Water Services - fictional water-pipe maintenance and service company</t>
         </is>
       </c>
     </row>
@@ -670,7 +670,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Leak Repair</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>HVAC scheduled or reactive task 001</t>
+          <t>Leak Repair scheduled or reactive task 001</t>
         </is>
       </c>
     </row>
@@ -725,7 +725,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Leak Repair</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -763,7 +763,7 @@
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>HVAC scheduled or reactive task 002</t>
+          <t>Leak Repair scheduled or reactive task 002</t>
         </is>
       </c>
     </row>
@@ -780,7 +780,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Leak Repair</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>HVAC scheduled or reactive task 003</t>
+          <t>Leak Repair scheduled or reactive task 003</t>
         </is>
       </c>
     </row>
@@ -833,7 +833,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Leak Repair</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>HVAC scheduled or reactive task 004</t>
+          <t>Leak Repair scheduled or reactive task 004</t>
         </is>
       </c>
     </row>
@@ -886,7 +886,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>Valve Repair</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>Electrical scheduled or reactive task 005</t>
+          <t>Valve Repair scheduled or reactive task 005</t>
         </is>
       </c>
     </row>
@@ -939,7 +939,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>Valve Repair</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>Electrical scheduled or reactive task 006</t>
+          <t>Valve Repair scheduled or reactive task 006</t>
         </is>
       </c>
     </row>
@@ -994,7 +994,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>Valve Repair</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>Electrical scheduled or reactive task 007</t>
+          <t>Valve Repair scheduled or reactive task 007</t>
         </is>
       </c>
     </row>
@@ -1049,7 +1049,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>Valve Repair</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1085,7 +1085,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>Electrical scheduled or reactive task 008</t>
+          <t>Valve Repair scheduled or reactive task 008</t>
         </is>
       </c>
     </row>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Plumbing</t>
+          <t>Pipe Replacement</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>Plumbing scheduled or reactive task 009</t>
+          <t>Pipe Replacement scheduled or reactive task 009</t>
         </is>
       </c>
     </row>
@@ -1155,7 +1155,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Plumbing</t>
+          <t>Pipe Replacement</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>Plumbing scheduled or reactive task 010</t>
+          <t>Pipe Replacement scheduled or reactive task 010</t>
         </is>
       </c>
     </row>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Plumbing</t>
+          <t>Pipe Replacement</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>Plumbing scheduled or reactive task 011</t>
+          <t>Pipe Replacement scheduled or reactive task 011</t>
         </is>
       </c>
     </row>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Plumbing</t>
+          <t>Pipe Replacement</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>Plumbing scheduled or reactive task 012</t>
+          <t>Pipe Replacement scheduled or reactive task 012</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety</t>
+          <t>Pump Service</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety scheduled or reactive task 013</t>
+          <t>Pump Service scheduled or reactive task 013</t>
         </is>
       </c>
     </row>
@@ -1367,7 +1367,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety</t>
+          <t>Pump Service</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety scheduled or reactive task 014</t>
+          <t>Pump Service scheduled or reactive task 014</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety</t>
+          <t>Pump Service</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety scheduled or reactive task 015</t>
+          <t>Pump Service scheduled or reactive task 015</t>
         </is>
       </c>
     </row>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety</t>
+          <t>Pump Service</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety scheduled or reactive task 016</t>
+          <t>Pump Service scheduled or reactive task 016</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>General Repair</t>
+          <t>Meter Service</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>General Repair scheduled or reactive task 017</t>
+          <t>Meter Service scheduled or reactive task 017</t>
         </is>
       </c>
     </row>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>General Repair</t>
+          <t>Meter Service</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>General Repair scheduled or reactive task 018</t>
+          <t>Meter Service scheduled or reactive task 018</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>General Repair</t>
+          <t>Meter Service</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>General Repair scheduled or reactive task 019</t>
+          <t>Meter Service scheduled or reactive task 019</t>
         </is>
       </c>
     </row>
@@ -1689,7 +1689,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>General Repair</t>
+          <t>Meter Service</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1725,7 +1725,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>General Repair scheduled or reactive task 020</t>
+          <t>Meter Service scheduled or reactive task 020</t>
         </is>
       </c>
     </row>
@@ -1742,7 +1742,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Leak Repair</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1780,7 +1780,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>HVAC scheduled or reactive task 021</t>
+          <t>Leak Repair scheduled or reactive task 021</t>
         </is>
       </c>
     </row>
@@ -1797,7 +1797,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Leak Repair</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>HVAC scheduled or reactive task 022</t>
+          <t>Leak Repair scheduled or reactive task 022</t>
         </is>
       </c>
     </row>
@@ -1852,7 +1852,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Leak Repair</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>HVAC scheduled or reactive task 023</t>
+          <t>Leak Repair scheduled or reactive task 023</t>
         </is>
       </c>
     </row>
@@ -1905,7 +1905,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Leak Repair</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>HVAC scheduled or reactive task 024</t>
+          <t>Leak Repair scheduled or reactive task 024</t>
         </is>
       </c>
     </row>
@@ -1958,7 +1958,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>Valve Repair</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1990,7 +1990,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>Electrical scheduled or reactive task 025</t>
+          <t>Valve Repair scheduled or reactive task 025</t>
         </is>
       </c>
     </row>
@@ -2007,7 +2007,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>Valve Repair</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -2045,7 +2045,7 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>Electrical scheduled or reactive task 026</t>
+          <t>Valve Repair scheduled or reactive task 026</t>
         </is>
       </c>
     </row>
@@ -2062,7 +2062,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>Valve Repair</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -2100,7 +2100,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>Electrical scheduled or reactive task 027</t>
+          <t>Valve Repair scheduled or reactive task 027</t>
         </is>
       </c>
     </row>
@@ -2117,7 +2117,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>Valve Repair</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -2153,7 +2153,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>Electrical scheduled or reactive task 028</t>
+          <t>Valve Repair scheduled or reactive task 028</t>
         </is>
       </c>
     </row>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Plumbing</t>
+          <t>Pipe Replacement</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>Plumbing scheduled or reactive task 029</t>
+          <t>Pipe Replacement scheduled or reactive task 029</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Plumbing</t>
+          <t>Pipe Replacement</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -2259,7 +2259,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>Plumbing scheduled or reactive task 030</t>
+          <t>Pipe Replacement scheduled or reactive task 030</t>
         </is>
       </c>
     </row>
@@ -2276,7 +2276,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Plumbing</t>
+          <t>Pipe Replacement</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -2314,7 +2314,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>Plumbing scheduled or reactive task 031</t>
+          <t>Pipe Replacement scheduled or reactive task 031</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Plumbing</t>
+          <t>Pipe Replacement</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>Plumbing scheduled or reactive task 032</t>
+          <t>Pipe Replacement scheduled or reactive task 032</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety</t>
+          <t>Pump Service</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -2422,7 +2422,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety scheduled or reactive task 033</t>
+          <t>Pump Service scheduled or reactive task 033</t>
         </is>
       </c>
     </row>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety</t>
+          <t>Pump Service</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -2475,7 +2475,7 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety scheduled or reactive task 034</t>
+          <t>Pump Service scheduled or reactive task 034</t>
         </is>
       </c>
     </row>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety</t>
+          <t>Pump Service</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -2528,7 +2528,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety scheduled or reactive task 035</t>
+          <t>Pump Service scheduled or reactive task 035</t>
         </is>
       </c>
     </row>
@@ -2545,7 +2545,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety</t>
+          <t>Pump Service</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -2583,7 +2583,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety scheduled or reactive task 036</t>
+          <t>Pump Service scheduled or reactive task 036</t>
         </is>
       </c>
     </row>
@@ -2600,7 +2600,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>General Repair</t>
+          <t>Meter Service</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>General Repair scheduled or reactive task 037</t>
+          <t>Meter Service scheduled or reactive task 037</t>
         </is>
       </c>
     </row>
@@ -2655,7 +2655,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>General Repair</t>
+          <t>Meter Service</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>General Repair scheduled or reactive task 038</t>
+          <t>Meter Service scheduled or reactive task 038</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>General Repair</t>
+          <t>Meter Service</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>General Repair scheduled or reactive task 039</t>
+          <t>Meter Service scheduled or reactive task 039</t>
         </is>
       </c>
     </row>
@@ -2761,7 +2761,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>General Repair</t>
+          <t>Meter Service</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -2797,7 +2797,7 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>General Repair scheduled or reactive task 040</t>
+          <t>Meter Service scheduled or reactive task 040</t>
         </is>
       </c>
     </row>
@@ -2814,7 +2814,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Leak Repair</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -2852,7 +2852,7 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>HVAC scheduled or reactive task 041</t>
+          <t>Leak Repair scheduled or reactive task 041</t>
         </is>
       </c>
     </row>
@@ -2869,7 +2869,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Leak Repair</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -2907,7 +2907,7 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>HVAC scheduled or reactive task 042</t>
+          <t>Leak Repair scheduled or reactive task 042</t>
         </is>
       </c>
     </row>
@@ -2924,7 +2924,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Leak Repair</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -2960,7 +2960,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>HVAC scheduled or reactive task 043</t>
+          <t>Leak Repair scheduled or reactive task 043</t>
         </is>
       </c>
     </row>
@@ -2977,7 +2977,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Leak Repair</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -3013,7 +3013,7 @@
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>HVAC scheduled or reactive task 044</t>
+          <t>Leak Repair scheduled or reactive task 044</t>
         </is>
       </c>
     </row>
@@ -3030,7 +3030,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>Valve Repair</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -3066,7 +3066,7 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>Electrical scheduled or reactive task 045</t>
+          <t>Valve Repair scheduled or reactive task 045</t>
         </is>
       </c>
     </row>
@@ -3083,7 +3083,7 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>Valve Repair</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>Electrical scheduled or reactive task 046</t>
+          <t>Valve Repair scheduled or reactive task 046</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>Valve Repair</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -3176,7 +3176,7 @@
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>Electrical scheduled or reactive task 047</t>
+          <t>Valve Repair scheduled or reactive task 047</t>
         </is>
       </c>
     </row>
@@ -3193,7 +3193,7 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>Valve Repair</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -3229,7 +3229,7 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>Electrical scheduled or reactive task 048</t>
+          <t>Valve Repair scheduled or reactive task 048</t>
         </is>
       </c>
     </row>
@@ -3246,7 +3246,7 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Plumbing</t>
+          <t>Pipe Replacement</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -3278,7 +3278,7 @@
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>Plumbing scheduled or reactive task 049</t>
+          <t>Pipe Replacement scheduled or reactive task 049</t>
         </is>
       </c>
     </row>
@@ -3295,7 +3295,7 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Plumbing</t>
+          <t>Pipe Replacement</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>Plumbing scheduled or reactive task 050</t>
+          <t>Pipe Replacement scheduled or reactive task 050</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Plumbing</t>
+          <t>Pipe Replacement</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>Plumbing scheduled or reactive task 051</t>
+          <t>Pipe Replacement scheduled or reactive task 051</t>
         </is>
       </c>
     </row>
@@ -3403,7 +3403,7 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Plumbing</t>
+          <t>Pipe Replacement</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -3441,7 +3441,7 @@
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>Plumbing scheduled or reactive task 052</t>
+          <t>Pipe Replacement scheduled or reactive task 052</t>
         </is>
       </c>
     </row>
@@ -3458,7 +3458,7 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety</t>
+          <t>Pump Service</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -3494,7 +3494,7 @@
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety scheduled or reactive task 053</t>
+          <t>Pump Service scheduled or reactive task 053</t>
         </is>
       </c>
     </row>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety</t>
+          <t>Pump Service</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -3547,7 +3547,7 @@
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety scheduled or reactive task 054</t>
+          <t>Pump Service scheduled or reactive task 054</t>
         </is>
       </c>
     </row>
@@ -3564,7 +3564,7 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety</t>
+          <t>Pump Service</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -3600,7 +3600,7 @@
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety scheduled or reactive task 055</t>
+          <t>Pump Service scheduled or reactive task 055</t>
         </is>
       </c>
     </row>
@@ -3617,7 +3617,7 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety</t>
+          <t>Pump Service</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -3655,7 +3655,7 @@
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety scheduled or reactive task 056</t>
+          <t>Pump Service scheduled or reactive task 056</t>
         </is>
       </c>
     </row>
@@ -3672,7 +3672,7 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>General Repair</t>
+          <t>Meter Service</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>General Repair scheduled or reactive task 057</t>
+          <t>Meter Service scheduled or reactive task 057</t>
         </is>
       </c>
     </row>
@@ -3727,7 +3727,7 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>General Repair</t>
+          <t>Meter Service</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>General Repair scheduled or reactive task 058</t>
+          <t>Meter Service scheduled or reactive task 058</t>
         </is>
       </c>
     </row>
@@ -3780,7 +3780,7 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>General Repair</t>
+          <t>Meter Service</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -3816,7 +3816,7 @@
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>General Repair scheduled or reactive task 059</t>
+          <t>Meter Service scheduled or reactive task 059</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3833,7 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>General Repair</t>
+          <t>Meter Service</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -3869,7 +3869,7 @@
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>General Repair scheduled or reactive task 060</t>
+          <t>Meter Service scheduled or reactive task 060</t>
         </is>
       </c>
     </row>
@@ -3886,7 +3886,7 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Leak Repair</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -3924,7 +3924,7 @@
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>HVAC scheduled or reactive task 061</t>
+          <t>Leak Repair scheduled or reactive task 061</t>
         </is>
       </c>
     </row>
@@ -3941,7 +3941,7 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Leak Repair</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -3979,7 +3979,7 @@
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>HVAC scheduled or reactive task 062</t>
+          <t>Leak Repair scheduled or reactive task 062</t>
         </is>
       </c>
     </row>
@@ -3996,7 +3996,7 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Leak Repair</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -4032,7 +4032,7 @@
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>HVAC scheduled or reactive task 063</t>
+          <t>Leak Repair scheduled or reactive task 063</t>
         </is>
       </c>
     </row>
@@ -4049,7 +4049,7 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Leak Repair</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -4085,7 +4085,7 @@
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>HVAC scheduled or reactive task 064</t>
+          <t>Leak Repair scheduled or reactive task 064</t>
         </is>
       </c>
     </row>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>Valve Repair</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -4138,7 +4138,7 @@
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>Electrical scheduled or reactive task 065</t>
+          <t>Valve Repair scheduled or reactive task 065</t>
         </is>
       </c>
     </row>
@@ -4155,7 +4155,7 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>Valve Repair</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>Electrical scheduled or reactive task 066</t>
+          <t>Valve Repair scheduled or reactive task 066</t>
         </is>
       </c>
     </row>
@@ -4210,7 +4210,7 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>Valve Repair</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -4248,7 +4248,7 @@
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>Electrical scheduled or reactive task 067</t>
+          <t>Valve Repair scheduled or reactive task 067</t>
         </is>
       </c>
     </row>
@@ -4265,7 +4265,7 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>Valve Repair</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>Electrical scheduled or reactive task 068</t>
+          <t>Valve Repair scheduled or reactive task 068</t>
         </is>
       </c>
     </row>
@@ -4318,7 +4318,7 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Plumbing</t>
+          <t>Pipe Replacement</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>Plumbing scheduled or reactive task 069</t>
+          <t>Pipe Replacement scheduled or reactive task 069</t>
         </is>
       </c>
     </row>
@@ -4371,7 +4371,7 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Plumbing</t>
+          <t>Pipe Replacement</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -4407,7 +4407,7 @@
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>Plumbing scheduled or reactive task 070</t>
+          <t>Pipe Replacement scheduled or reactive task 070</t>
         </is>
       </c>
     </row>
@@ -4424,7 +4424,7 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Plumbing</t>
+          <t>Pipe Replacement</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -4462,7 +4462,7 @@
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>Plumbing scheduled or reactive task 071</t>
+          <t>Pipe Replacement scheduled or reactive task 071</t>
         </is>
       </c>
     </row>
@@ -4479,7 +4479,7 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Plumbing</t>
+          <t>Pipe Replacement</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -4517,7 +4517,7 @@
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>Plumbing scheduled or reactive task 072</t>
+          <t>Pipe Replacement scheduled or reactive task 072</t>
         </is>
       </c>
     </row>
@@ -4534,7 +4534,7 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety</t>
+          <t>Pump Service</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -4566,7 +4566,7 @@
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety scheduled or reactive task 073</t>
+          <t>Pump Service scheduled or reactive task 073</t>
         </is>
       </c>
     </row>
@@ -4583,7 +4583,7 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety</t>
+          <t>Pump Service</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -4619,7 +4619,7 @@
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety scheduled or reactive task 074</t>
+          <t>Pump Service scheduled or reactive task 074</t>
         </is>
       </c>
     </row>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety</t>
+          <t>Pump Service</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -4672,7 +4672,7 @@
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety scheduled or reactive task 075</t>
+          <t>Pump Service scheduled or reactive task 075</t>
         </is>
       </c>
     </row>
@@ -4689,7 +4689,7 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety</t>
+          <t>Pump Service</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -4727,7 +4727,7 @@
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety scheduled or reactive task 076</t>
+          <t>Pump Service scheduled or reactive task 076</t>
         </is>
       </c>
     </row>
@@ -4744,7 +4744,7 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>General Repair</t>
+          <t>Meter Service</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -4782,7 +4782,7 @@
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>General Repair scheduled or reactive task 077</t>
+          <t>Meter Service scheduled or reactive task 077</t>
         </is>
       </c>
     </row>
@@ -4799,7 +4799,7 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>General Repair</t>
+          <t>Meter Service</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
@@ -4835,7 +4835,7 @@
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>General Repair scheduled or reactive task 078</t>
+          <t>Meter Service scheduled or reactive task 078</t>
         </is>
       </c>
     </row>
@@ -4852,7 +4852,7 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>General Repair</t>
+          <t>Meter Service</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -4888,7 +4888,7 @@
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>General Repair scheduled or reactive task 079</t>
+          <t>Meter Service scheduled or reactive task 079</t>
         </is>
       </c>
     </row>
@@ -4905,7 +4905,7 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>General Repair</t>
+          <t>Meter Service</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>General Repair scheduled or reactive task 080</t>
+          <t>Meter Service scheduled or reactive task 080</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Leak Repair</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
@@ -4996,7 +4996,7 @@
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>HVAC scheduled or reactive task 081</t>
+          <t>Leak Repair scheduled or reactive task 081</t>
         </is>
       </c>
     </row>
@@ -5013,7 +5013,7 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Leak Repair</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>HVAC scheduled or reactive task 082</t>
+          <t>Leak Repair scheduled or reactive task 082</t>
         </is>
       </c>
     </row>
@@ -5068,7 +5068,7 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Leak Repair</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
@@ -5104,7 +5104,7 @@
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>HVAC scheduled or reactive task 083</t>
+          <t>Leak Repair scheduled or reactive task 083</t>
         </is>
       </c>
     </row>
@@ -5121,7 +5121,7 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Leak Repair</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
@@ -5157,7 +5157,7 @@
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>HVAC scheduled or reactive task 084</t>
+          <t>Leak Repair scheduled or reactive task 084</t>
         </is>
       </c>
     </row>
@@ -5174,7 +5174,7 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>Valve Repair</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
@@ -5206,7 +5206,7 @@
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>Electrical scheduled or reactive task 085</t>
+          <t>Valve Repair scheduled or reactive task 085</t>
         </is>
       </c>
     </row>
@@ -5223,7 +5223,7 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>Valve Repair</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
@@ -5261,7 +5261,7 @@
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>Electrical scheduled or reactive task 086</t>
+          <t>Valve Repair scheduled or reactive task 086</t>
         </is>
       </c>
     </row>
@@ -5278,7 +5278,7 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>Valve Repair</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>Electrical scheduled or reactive task 087</t>
+          <t>Valve Repair scheduled or reactive task 087</t>
         </is>
       </c>
     </row>
@@ -5333,7 +5333,7 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>Valve Repair</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
@@ -5369,7 +5369,7 @@
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>Electrical scheduled or reactive task 088</t>
+          <t>Valve Repair scheduled or reactive task 088</t>
         </is>
       </c>
     </row>
@@ -5386,7 +5386,7 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Plumbing</t>
+          <t>Pipe Replacement</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
@@ -5422,7 +5422,7 @@
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>Plumbing scheduled or reactive task 089</t>
+          <t>Pipe Replacement scheduled or reactive task 089</t>
         </is>
       </c>
     </row>
@@ -5439,7 +5439,7 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Plumbing</t>
+          <t>Pipe Replacement</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
@@ -5475,7 +5475,7 @@
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>Plumbing scheduled or reactive task 090</t>
+          <t>Pipe Replacement scheduled or reactive task 090</t>
         </is>
       </c>
     </row>
@@ -5492,7 +5492,7 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Plumbing</t>
+          <t>Pipe Replacement</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
@@ -5530,7 +5530,7 @@
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>Plumbing scheduled or reactive task 091</t>
+          <t>Pipe Replacement scheduled or reactive task 091</t>
         </is>
       </c>
     </row>
@@ -5547,7 +5547,7 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Plumbing</t>
+          <t>Pipe Replacement</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
@@ -5585,7 +5585,7 @@
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>Plumbing scheduled or reactive task 092</t>
+          <t>Pipe Replacement scheduled or reactive task 092</t>
         </is>
       </c>
     </row>
@@ -5602,7 +5602,7 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety</t>
+          <t>Pump Service</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
@@ -5638,7 +5638,7 @@
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety scheduled or reactive task 093</t>
+          <t>Pump Service scheduled or reactive task 093</t>
         </is>
       </c>
     </row>
@@ -5655,7 +5655,7 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety</t>
+          <t>Pump Service</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
@@ -5691,7 +5691,7 @@
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety scheduled or reactive task 094</t>
+          <t>Pump Service scheduled or reactive task 094</t>
         </is>
       </c>
     </row>
@@ -5708,7 +5708,7 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety</t>
+          <t>Pump Service</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
@@ -5744,7 +5744,7 @@
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety scheduled or reactive task 095</t>
+          <t>Pump Service scheduled or reactive task 095</t>
         </is>
       </c>
     </row>
@@ -5761,7 +5761,7 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety</t>
+          <t>Pump Service</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
@@ -5799,7 +5799,7 @@
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety scheduled or reactive task 096</t>
+          <t>Pump Service scheduled or reactive task 096</t>
         </is>
       </c>
     </row>
@@ -5816,7 +5816,7 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>General Repair</t>
+          <t>Meter Service</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
@@ -5854,7 +5854,7 @@
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>General Repair scheduled or reactive task 097</t>
+          <t>Meter Service scheduled or reactive task 097</t>
         </is>
       </c>
     </row>
@@ -5871,7 +5871,7 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>General Repair</t>
+          <t>Meter Service</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
@@ -5907,7 +5907,7 @@
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>General Repair scheduled or reactive task 098</t>
+          <t>Meter Service scheduled or reactive task 098</t>
         </is>
       </c>
     </row>
@@ -5924,7 +5924,7 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>General Repair</t>
+          <t>Meter Service</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
@@ -5960,7 +5960,7 @@
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>General Repair scheduled or reactive task 099</t>
+          <t>Meter Service scheduled or reactive task 099</t>
         </is>
       </c>
     </row>
@@ -5977,7 +5977,7 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>General Repair</t>
+          <t>Meter Service</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
@@ -6013,7 +6013,7 @@
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>General Repair scheduled or reactive task 100</t>
+          <t>Meter Service scheduled or reactive task 100</t>
         </is>
       </c>
     </row>
@@ -6030,7 +6030,7 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Leak Repair</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
@@ -6068,7 +6068,7 @@
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>HVAC scheduled or reactive task 101</t>
+          <t>Leak Repair scheduled or reactive task 101</t>
         </is>
       </c>
     </row>
@@ -6085,7 +6085,7 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Leak Repair</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
@@ -6123,7 +6123,7 @@
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t>HVAC scheduled or reactive task 102</t>
+          <t>Leak Repair scheduled or reactive task 102</t>
         </is>
       </c>
     </row>
@@ -6140,7 +6140,7 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Leak Repair</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
@@ -6176,7 +6176,7 @@
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>HVAC scheduled or reactive task 103</t>
+          <t>Leak Repair scheduled or reactive task 103</t>
         </is>
       </c>
     </row>
@@ -6193,7 +6193,7 @@
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Leak Repair</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
@@ -6229,7 +6229,7 @@
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
-          <t>HVAC scheduled or reactive task 104</t>
+          <t>Leak Repair scheduled or reactive task 104</t>
         </is>
       </c>
     </row>
@@ -6246,7 +6246,7 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>Valve Repair</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
@@ -6282,7 +6282,7 @@
       </c>
       <c r="M106" s="2" t="inlineStr">
         <is>
-          <t>Electrical scheduled or reactive task 105</t>
+          <t>Valve Repair scheduled or reactive task 105</t>
         </is>
       </c>
     </row>
@@ -6299,7 +6299,7 @@
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>Valve Repair</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
@@ -6337,7 +6337,7 @@
       </c>
       <c r="M107" s="2" t="inlineStr">
         <is>
-          <t>Electrical scheduled or reactive task 106</t>
+          <t>Valve Repair scheduled or reactive task 106</t>
         </is>
       </c>
     </row>
@@ -6354,7 +6354,7 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>Valve Repair</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
@@ -6392,7 +6392,7 @@
       </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
-          <t>Electrical scheduled or reactive task 107</t>
+          <t>Valve Repair scheduled or reactive task 107</t>
         </is>
       </c>
     </row>
@@ -6409,7 +6409,7 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>Valve Repair</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
@@ -6445,7 +6445,7 @@
       </c>
       <c r="M109" s="2" t="inlineStr">
         <is>
-          <t>Electrical scheduled or reactive task 108</t>
+          <t>Valve Repair scheduled or reactive task 108</t>
         </is>
       </c>
     </row>
@@ -6462,7 +6462,7 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Plumbing</t>
+          <t>Pipe Replacement</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
@@ -6494,7 +6494,7 @@
       </c>
       <c r="M110" s="2" t="inlineStr">
         <is>
-          <t>Plumbing scheduled or reactive task 109</t>
+          <t>Pipe Replacement scheduled or reactive task 109</t>
         </is>
       </c>
     </row>
@@ -6511,7 +6511,7 @@
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>Plumbing</t>
+          <t>Pipe Replacement</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
@@ -6547,7 +6547,7 @@
       </c>
       <c r="M111" s="2" t="inlineStr">
         <is>
-          <t>Plumbing scheduled or reactive task 110</t>
+          <t>Pipe Replacement scheduled or reactive task 110</t>
         </is>
       </c>
     </row>
@@ -6564,7 +6564,7 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>Plumbing</t>
+          <t>Pipe Replacement</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
@@ -6602,7 +6602,7 @@
       </c>
       <c r="M112" s="2" t="inlineStr">
         <is>
-          <t>Plumbing scheduled or reactive task 111</t>
+          <t>Pipe Replacement scheduled or reactive task 111</t>
         </is>
       </c>
     </row>
@@ -6619,7 +6619,7 @@
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>Plumbing</t>
+          <t>Pipe Replacement</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
@@ -6657,7 +6657,7 @@
       </c>
       <c r="M113" s="2" t="inlineStr">
         <is>
-          <t>Plumbing scheduled or reactive task 112</t>
+          <t>Pipe Replacement scheduled or reactive task 112</t>
         </is>
       </c>
     </row>
@@ -6674,7 +6674,7 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety</t>
+          <t>Pump Service</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
@@ -6710,7 +6710,7 @@
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety scheduled or reactive task 113</t>
+          <t>Pump Service scheduled or reactive task 113</t>
         </is>
       </c>
     </row>
@@ -6727,7 +6727,7 @@
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety</t>
+          <t>Pump Service</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
@@ -6763,7 +6763,7 @@
       </c>
       <c r="M115" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety scheduled or reactive task 114</t>
+          <t>Pump Service scheduled or reactive task 114</t>
         </is>
       </c>
     </row>
@@ -6780,7 +6780,7 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety</t>
+          <t>Pump Service</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="M116" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety scheduled or reactive task 115</t>
+          <t>Pump Service scheduled or reactive task 115</t>
         </is>
       </c>
     </row>
@@ -6833,7 +6833,7 @@
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety</t>
+          <t>Pump Service</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
@@ -6871,7 +6871,7 @@
       </c>
       <c r="M117" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety scheduled or reactive task 116</t>
+          <t>Pump Service scheduled or reactive task 116</t>
         </is>
       </c>
     </row>
@@ -6888,7 +6888,7 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>General Repair</t>
+          <t>Meter Service</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
@@ -6926,7 +6926,7 @@
       </c>
       <c r="M118" s="2" t="inlineStr">
         <is>
-          <t>General Repair scheduled or reactive task 117</t>
+          <t>Meter Service scheduled or reactive task 117</t>
         </is>
       </c>
     </row>
@@ -6943,7 +6943,7 @@
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>General Repair</t>
+          <t>Meter Service</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
@@ -6979,7 +6979,7 @@
       </c>
       <c r="M119" s="2" t="inlineStr">
         <is>
-          <t>General Repair scheduled or reactive task 118</t>
+          <t>Meter Service scheduled or reactive task 118</t>
         </is>
       </c>
     </row>
@@ -6996,7 +6996,7 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>General Repair</t>
+          <t>Meter Service</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
@@ -7032,7 +7032,7 @@
       </c>
       <c r="M120" s="2" t="inlineStr">
         <is>
-          <t>General Repair scheduled or reactive task 119</t>
+          <t>Meter Service scheduled or reactive task 119</t>
         </is>
       </c>
     </row>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>General Repair</t>
+          <t>Meter Service</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
@@ -7085,7 +7085,7 @@
       </c>
       <c r="M121" s="2" t="inlineStr">
         <is>
-          <t>General Repair scheduled or reactive task 120</t>
+          <t>Meter Service scheduled or reactive task 120</t>
         </is>
       </c>
     </row>
@@ -7143,7 +7143,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Leak Repair</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
@@ -7163,7 +7163,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Leak Repair</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
@@ -7183,7 +7183,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Leak Repair</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
@@ -7203,7 +7203,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Leak Repair</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
@@ -7223,7 +7223,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>Valve Repair</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
@@ -7243,7 +7243,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>Valve Repair</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
@@ -7263,7 +7263,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>Valve Repair</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
@@ -7283,7 +7283,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>Valve Repair</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
@@ -7489,7 +7489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -7535,69 +7535,105 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>Step 1</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>EXCEL - CHAT ONLY</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>EXCEL - CHAT ONLY:
+Inspect this Northstar Water Services dashboard starter. Confirm tblWorkOrders, 120 unique IDs, reporting date 2026-09-30 and selection cells B2:B5 initially All. Explain which source and control sheets must remain intact. Report discrepancies before any edits.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
           <t>Step 2</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>EXCEL - PLAN</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>EXCEL - PLAN:
 Plan Dashboard for Northstar maintenance at 2026-09-30. Use selection cells B2:B5 for Site, Job_Category, Status, Assigned_To, all initially All. Reserve B7 total orders, B8 backlog, B9 overdue backlog, B10 closed, B11 on-time closure rate, B12 Cost_SGD. Place three charts for status, category and site with labels, units and scope. Preserve source data.</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Step 3</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>EXCEL - ALLOW EDITING</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>EXCEL - ALLOW EDITING:
 Build the planned six KPI formulas from tblWorkOrders. Backlog excludes Closed/Cancelled. Overdue also requires Due_Date &lt; Control!B2. On-time rate counts Closed_Date &lt;= Due_Date among Closed rows only, and shows N/A when none. Recorded cost sums Cost_SGD of all included statuses. Link to table columns, never a fixed 120-row range. Keep source data unchanged.</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Step 4</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>EXCEL - ALLOW EDITING</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>EXCEL - ALLOW EDITING:
 Create three editable bar or column charts using formula-backed summaries: work-order count by Status, by Job_Category and by Site. Each summary must reconcile to the total selected orders. Use white background, navy titles, blue/teal accents, readable labels and a visible reporting date. Do not use category counts as evidence of causes or use colour alone for status.</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Step 5</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>EXCEL - CHAT ONLY</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>EXCEL - CHAT ONLY:
+Reconcile the Northstar Water Services dashboard with Control at All selections. Compare all six KPIs and totals of the Status, Job_Category and Site charts. Flag hard-coded values, fixed row ranges, inconsistent scopes and any interpretation that treats job-category frequency as a cause. Do not edit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Step 6</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>EXCEL - CHAT ONLY</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>EXCEL - CHAT ONLY:
 Explain each Dashboard measure in plain English, including terminal statuses, strict overdue date rule, closed-only SLA denominator and meaning of recorded cost. Give one source-row example for overdue and one for on-time closure; cite Work_Order_ID. Do not guess a root cause or financial saving.</t>
